--- a/begunici/app_types/animals/excel_templates/import/import_vet.xlsx
+++ b/begunici/app_types/animals/excel_templates/import/import_vet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim\Desktop\begunici\begunici\app_types\animals\excel_templates\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DB943D-8998-4A45-B08D-010F67A52F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C1B917-B7B8-4E55-8CCE-CD61F647124B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3697" windowWidth="16200" windowHeight="9983" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
     <t>Дата обработки (ЧЧ-ММ-ГГ)</t>
   </si>
   <si>
-    <t>№ обработки (число из справки)</t>
+    <t>№ обработки (число из справки, можно несколько через запятую)</t>
   </si>
 </sst>
 </file>
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +126,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -421,14 +424,14 @@
     <col min="10" max="10" width="16.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
